--- a/artfynd/A 11623-2024 artfynd.xlsx
+++ b/artfynd/A 11623-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126795748</v>
       </c>
       <c r="B2" t="n">
-        <v>44799</v>
+        <v>44803</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>126795736</v>
       </c>
       <c r="B3" t="n">
-        <v>44790</v>
+        <v>44794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11623-2024 artfynd.xlsx
+++ b/artfynd/A 11623-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126795748</v>
       </c>
       <c r="B2" t="n">
-        <v>44803</v>
+        <v>44799</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>126795736</v>
       </c>
       <c r="B3" t="n">
-        <v>44794</v>
+        <v>44790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11623-2024 artfynd.xlsx
+++ b/artfynd/A 11623-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126795748</v>
+        <v>126795736</v>
       </c>
       <c r="B2" t="n">
-        <v>44803</v>
+        <v>45033</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>201164</v>
+        <v>102366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sexfläckig bastardsvärmare</t>
+          <t>Ängsmetallvinge</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zygaena filipendulae</t>
+          <t>Adscita statices</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,11 +703,27 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -792,27 +808,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126795736</v>
+        <v>126795748</v>
       </c>
       <c r="B3" t="n">
-        <v>44794</v>
+        <v>45042</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102366</v>
+        <v>201164</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ängsmetallvinge</t>
+          <t>Sexfläckig bastardsvärmare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Adscita statices</t>
+          <t>Zygaena filipendulae</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -820,27 +836,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>observerad</t>

--- a/artfynd/A 11623-2024 artfynd.xlsx
+++ b/artfynd/A 11623-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -805,6 +810,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126795736</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,8 +932,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126795748</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>